--- a/49796_Cuenca_Itaya/_raw_reportes_xlsx/IDConfig_65338_completo.xlsx
+++ b/49796_Cuenca_Itaya/_raw_reportes_xlsx/IDConfig_65338_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rcfb26656cd9e4e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R346cba30e6da4b7c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.7300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49796_Cuenca_Itaya/_raw_reportes_xlsx/IDConfig_65338_completo.xlsx
+++ b/49796_Cuenca_Itaya/_raw_reportes_xlsx/IDConfig_65338_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R346cba30e6da4b7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R822d938e07c443af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,711 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.8900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.8900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    108.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
